--- a/Petty cash.xlsx
+++ b/Petty cash.xlsx
@@ -26,12 +26,8 @@
 </workbook>
 </file>
 
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>Tanggal</t>
   </si>
@@ -169,6 +165,15 @@
   </si>
   <si>
     <t>REIMBURSE PURCHASE OF CHICKEN LEG AT 30 DEC 2025 TO CHEF RISKI REGARDING URGENT SUPPLIES</t>
+  </si>
+  <si>
+    <t>TRANSFER KE SIGID PURNAMA</t>
+  </si>
+  <si>
+    <t>REIMBURSING PURCHASE OF 1X AQUA GALLOON FOR BAR TO SIGID PURNAMA</t>
+  </si>
+  <si>
+    <t>PURCHASE 5 PACK OF TORTILLA WRAP DELIVERED BY GOSEND</t>
   </si>
 </sst>
 </file>
@@ -1998,6 +2003,84 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>27305</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2205355</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2703830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_D73B6F21FFC541589EF6BAFFE966BA49" descr="PHOTO-2026-01-02-14-09-59"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:srcRect t="16111" r="8304" b="21795"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11964670" y="47382430"/>
+          <a:ext cx="2178050" cy="2678430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>27305</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2207260</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2819400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_7B5079D33D0F4480A3BA0A1F1B121E9C" descr="PHOTO-2026-01-02-15-32-36"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:srcRect t="10006" r="740" b="19985"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11962765" y="50107850"/>
+          <a:ext cx="2181860" cy="2792095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2389,7 +2472,7 @@
         <v>22500</v>
       </c>
       <c r="E3" s="11">
-        <f t="shared" ref="E3:E19" si="0">E2+C3-D3</f>
+        <f t="shared" ref="E3:E33" si="0">E2+C3-D3</f>
         <v>508098</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -2731,30 +2814,47 @@
       <c r="G19" s="19"/>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
+    <row r="20" customFormat="1" ht="214.45" customHeight="1" spans="1:14">
+      <c r="A20" s="6">
+        <v>46024</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="D20" s="8">
+        <v>29475</v>
+      </c>
       <c r="E20" s="11">
-        <f>E19+C20-D20</f>
-        <v>1331718</v>
-      </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24"/>
+        <f t="shared" si="0"/>
+        <v>1302243</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="I20" s="21"/>
       <c r="N20" s="2"/>
     </row>
-    <row r="21" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
+    <row r="21" customFormat="1" ht="223.2" customHeight="1" spans="1:14">
+      <c r="A21" s="6">
+        <v>46024</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="D21" s="8">
+        <v>236500</v>
+      </c>
       <c r="E21" s="11">
-        <f>E20+C21-D21</f>
-        <v>1331718</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="24"/>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="19"/>
       <c r="N21" s="2"/>
     </row>
     <row r="22" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
@@ -2763,8 +2863,8 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="11">
-        <f>E21+C22-D22</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="24"/>
@@ -2776,8 +2876,8 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="11">
-        <f>E22+C23-D23</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="24"/>
@@ -2789,8 +2889,8 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="11">
-        <f>E23+C24-D24</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="24"/>
@@ -2802,8 +2902,8 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="11">
-        <f>E24+C25-D25</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F25" s="23"/>
       <c r="G25" s="24"/>
@@ -2815,8 +2915,8 @@
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="11">
-        <f>E25+C26-D26</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F26" s="23"/>
       <c r="G26" s="24"/>
@@ -2828,8 +2928,8 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="11">
-        <f>E26+C27-D27</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="24"/>
@@ -2841,8 +2941,8 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="11">
-        <f>E27+C28-D28</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="24"/>
@@ -2854,8 +2954,8 @@
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="11">
-        <f>E28+C29-D29</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F29" s="23"/>
       <c r="G29" s="24"/>
@@ -2867,8 +2967,8 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="11">
-        <f>E29+C30-D30</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F30" s="23"/>
       <c r="G30" s="24"/>
@@ -2880,8 +2980,8 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="11">
-        <f>E30+C31-D31</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F31" s="23"/>
       <c r="G31" s="24"/>
@@ -2893,8 +2993,8 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="11">
-        <f>E31+C32-D32</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F32" s="23"/>
       <c r="G32" s="24"/>
@@ -2906,8 +3006,8 @@
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="11">
-        <f>E32+C33-D33</f>
-        <v>1331718</v>
+        <f t="shared" si="0"/>
+        <v>1065743</v>
       </c>
       <c r="F33" s="23"/>
       <c r="G33" s="24"/>
